--- a/lots.xlsx
+++ b/lots.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathi\Documents\CS\tombola\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathi\Documents\CS\tirage_au_sort_tombola\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C2F9C3-2171-4322-883B-962B5E03C68E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04AEBAFD-B1A8-4A58-BDDF-0519F35E0A36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="47">
   <si>
     <t>lots</t>
   </si>
@@ -128,6 +128,39 @@
   </si>
   <si>
     <t>Oliver Wyman</t>
+  </si>
+  <si>
+    <t>du pre-shotgun pistus 2x</t>
+  </si>
+  <si>
+    <t>du pre-shotgun pistus 3x</t>
+  </si>
+  <si>
+    <t>du pre-shotgun pistus 4x</t>
+  </si>
+  <si>
+    <t>du pre-shotgun pistus 5x</t>
+  </si>
+  <si>
+    <t>du pre-shotgun pistus 6x</t>
+  </si>
+  <si>
+    <t>du pre-shotgun pistus 7x</t>
+  </si>
+  <si>
+    <t>du pre-shotgun pistus 8x</t>
+  </si>
+  <si>
+    <t>du pre-shotgun pistus x9</t>
+  </si>
+  <si>
+    <t>du pre-shotgun pistus 10x</t>
+  </si>
+  <si>
+    <t>de l'appareil à fondue</t>
+  </si>
+  <si>
+    <t>de l'appareil à raclette</t>
   </si>
 </sst>
 </file>
@@ -490,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
@@ -504,17 +537,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
@@ -522,7 +547,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
@@ -530,15 +555,15 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
@@ -546,7 +571,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
@@ -554,15 +579,15 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
         <v>5</v>
@@ -570,7 +595,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
         <v>5</v>
@@ -578,58 +603,58 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.45">
@@ -642,7 +667,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
@@ -650,7 +675,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B20" t="s">
         <v>12</v>
@@ -658,17 +683,113 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
         <v>34</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B34" t="s">
         <v>35</v>
       </c>
     </row>

--- a/lots.xlsx
+++ b/lots.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathi\Documents\CS\tirage_au_sort_tombola\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04AEBAFD-B1A8-4A58-BDDF-0519F35E0A36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2789D0C-8657-4327-A1AB-5706CB28462B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="428" windowWidth="19140" windowHeight="12352" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="48">
   <si>
     <t>lots</t>
   </si>
@@ -161,6 +161,9 @@
   </si>
   <si>
     <t>de l'appareil à raclette</t>
+  </si>
+  <si>
+    <t>personne</t>
   </si>
 </sst>
 </file>
@@ -544,6 +547,9 @@
       <c r="B3" t="s">
         <v>3</v>
       </c>
+      <c r="C3" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
@@ -552,6 +558,9 @@
       <c r="B4" t="s">
         <v>3</v>
       </c>
+      <c r="C4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
@@ -560,6 +569,9 @@
       <c r="B5" t="s">
         <v>3</v>
       </c>
+      <c r="C5" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
@@ -568,6 +580,9 @@
       <c r="B6" t="s">
         <v>4</v>
       </c>
+      <c r="C6" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
@@ -576,6 +591,9 @@
       <c r="B7" t="s">
         <v>4</v>
       </c>
+      <c r="C7" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
@@ -584,6 +602,9 @@
       <c r="B8" t="s">
         <v>4</v>
       </c>
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
@@ -592,6 +613,9 @@
       <c r="B9" t="s">
         <v>5</v>
       </c>
+      <c r="C9" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
@@ -600,6 +624,9 @@
       <c r="B10" t="s">
         <v>5</v>
       </c>
+      <c r="C10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
@@ -608,6 +635,9 @@
       <c r="B11" t="s">
         <v>5</v>
       </c>
+      <c r="C11" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
@@ -616,6 +646,9 @@
       <c r="B12" t="s">
         <v>6</v>
       </c>
+      <c r="C12" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
@@ -624,6 +657,9 @@
       <c r="B13" t="s">
         <v>7</v>
       </c>
+      <c r="C13" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
@@ -632,6 +668,9 @@
       <c r="B14" t="s">
         <v>8</v>
       </c>
+      <c r="C14" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
@@ -640,6 +679,9 @@
       <c r="B15" t="s">
         <v>9</v>
       </c>
+      <c r="C15" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
@@ -648,149 +690,206 @@
       <c r="B16" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>28</v>
       </c>
       <c r="B17" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>30</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>29</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C19" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>31</v>
       </c>
       <c r="B20" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>36</v>
       </c>
       <c r="B21" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C21" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>37</v>
       </c>
       <c r="B22" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>38</v>
       </c>
       <c r="B23" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C23" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>39</v>
       </c>
       <c r="B24" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>40</v>
       </c>
       <c r="B25" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C25" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>41</v>
       </c>
       <c r="B26" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C26" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>42</v>
       </c>
       <c r="B27" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C27" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>43</v>
       </c>
       <c r="B28" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C28" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>44</v>
       </c>
       <c r="B29" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C29" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>32</v>
       </c>
       <c r="B30" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C30" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>45</v>
       </c>
       <c r="B31" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C31" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>46</v>
       </c>
       <c r="B32" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>33</v>
       </c>
       <c r="B33" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C33" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>34</v>
       </c>
       <c r="B34" t="s">
         <v>35</v>
+      </c>
+      <c r="C34" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/lots.xlsx
+++ b/lots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathi\Documents\CS\tirage_au_sort_tombola\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2789D0C-8657-4327-A1AB-5706CB28462B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F49A58FD-FCE8-4AB7-B16A-E673195807D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1837" yWindow="428" windowWidth="19140" windowHeight="12352" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="49">
   <si>
     <t>lots</t>
   </si>
@@ -164,6 +164,9 @@
   </si>
   <si>
     <t>personne</t>
+  </si>
+  <si>
+    <t>d'un panier Miam Localpersonne</t>
   </si>
 </sst>
 </file>
@@ -526,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
@@ -696,10 +699,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="C17" t="s">
         <v>47</v>
@@ -707,10 +707,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C18" t="s">
         <v>47</v>
@@ -718,10 +718,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
         <v>47</v>
@@ -729,7 +729,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B20" t="s">
         <v>12</v>
@@ -740,7 +740,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B21" t="s">
         <v>12</v>
@@ -751,7 +751,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B22" t="s">
         <v>12</v>
@@ -762,7 +762,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" t="s">
         <v>12</v>
@@ -773,7 +773,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24" t="s">
         <v>12</v>
@@ -784,7 +784,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25" t="s">
         <v>12</v>
@@ -795,7 +795,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B26" t="s">
         <v>12</v>
@@ -806,7 +806,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B27" t="s">
         <v>12</v>
@@ -817,7 +817,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B28" t="s">
         <v>12</v>
@@ -828,7 +828,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B29" t="s">
         <v>12</v>
@@ -839,7 +839,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B30" t="s">
         <v>12</v>
@@ -850,7 +850,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="B31" t="s">
         <v>12</v>
@@ -861,7 +861,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B32" t="s">
         <v>12</v>
@@ -872,10 +872,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="B33" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C33" t="s">
         <v>47</v>
@@ -883,12 +883,23 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B34" t="s">
         <v>35</v>
       </c>
       <c r="C34" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" t="s">
         <v>47</v>
       </c>
     </row>

--- a/lots.xlsx
+++ b/lots.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathi\Documents\CS\tirage_au_sort_tombola\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F49A58FD-FCE8-4AB7-B16A-E673195807D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB460C23-D7AA-4D3A-9734-749005CFE3E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="428" windowWidth="19140" windowHeight="12352" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2460" yWindow="428" windowWidth="19140" windowHeight="12352" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="62">
   <si>
     <t>lots</t>
   </si>
@@ -31,142 +31,181 @@
     <t>gagnants</t>
   </si>
   <si>
+    <t>du Livre : "La colère"</t>
+  </si>
+  <si>
     <t>BDA</t>
   </si>
   <si>
+    <t>du Livre : "Chienne de vie"</t>
+  </si>
+  <si>
+    <t>du Livre : "sous les feux d'artifice"</t>
+  </si>
+  <si>
+    <t>du 1er sac de sport de promo</t>
+  </si>
+  <si>
     <t>BDE</t>
   </si>
   <si>
+    <t>du 2ème sac de sport de promo</t>
+  </si>
+  <si>
+    <t>du 3ème sac de sport de promo</t>
+  </si>
+  <si>
+    <t>du 1er bon de 5€ pour pépins</t>
+  </si>
+  <si>
     <t>Impact</t>
   </si>
   <si>
+    <t>du 2ème bon de 5€ pour pépins</t>
+  </si>
+  <si>
+    <t>du 3ème bon de 5€ pour pépins</t>
+  </si>
+  <si>
+    <t>des Chocolats Nepal</t>
+  </si>
+  <si>
     <t>FIR</t>
   </si>
   <si>
+    <t>des 2 places pour le NND</t>
+  </si>
+  <si>
     <t>RAID</t>
   </si>
   <si>
+    <t>des 2 places pour la commu's</t>
+  </si>
+  <si>
     <t>Commu's</t>
   </si>
   <si>
+    <t>de la place pour le TOSS</t>
+  </si>
+  <si>
     <t>BDS</t>
   </si>
   <si>
+    <t>des impressions de 5 photos</t>
+  </si>
+  <si>
     <t>PICS</t>
   </si>
   <si>
+    <t>du casque audio ou de la cotiz VR</t>
+  </si>
+  <si>
     <t>Viarezo</t>
   </si>
   <si>
+    <t>de la Bouteille de champagne</t>
+  </si>
+  <si>
+    <t>JCS</t>
+  </si>
+  <si>
+    <t>du Bonnet</t>
+  </si>
+  <si>
     <t>WACS</t>
   </si>
   <si>
-    <t>JCS</t>
-  </si>
-  <si>
-    <t>du Livre : "La colère"</t>
-  </si>
-  <si>
-    <t>du Livre : "Chienne de vie"</t>
-  </si>
-  <si>
-    <t>du Livre : "sous les feux d'artifice"</t>
-  </si>
-  <si>
-    <t>du 1er sac de sport de promo</t>
-  </si>
-  <si>
-    <t>du 2ème sac de sport de promo</t>
-  </si>
-  <si>
-    <t>du 3ème sac de sport de promo</t>
-  </si>
-  <si>
-    <t>du 1er bon de 5€ pour pépins</t>
-  </si>
-  <si>
-    <t>du 2ème bon de 5€ pour pépins</t>
-  </si>
-  <si>
-    <t>du 3ème bon de 5€ pour pépins</t>
-  </si>
-  <si>
-    <t>des Chocolats Nepal</t>
-  </si>
-  <si>
-    <t>des 2 places pour le NND</t>
-  </si>
-  <si>
-    <t>des 2 places pour la commu's</t>
-  </si>
-  <si>
-    <t>de la place pour le TOSS</t>
-  </si>
-  <si>
-    <t>des impressions de 5 photos</t>
-  </si>
-  <si>
-    <t>du casque audio ou de la cotiz VR</t>
-  </si>
-  <si>
-    <t>du Bonnet</t>
-  </si>
-  <si>
-    <t>de la Bouteille de champagne</t>
-  </si>
-  <si>
     <t>du pre-shotgun pistus 1x</t>
   </si>
   <si>
+    <t>du pre-shotgun pistus 2x</t>
+  </si>
+  <si>
+    <t>du pre-shotgun pistus 3x</t>
+  </si>
+  <si>
+    <t>du pre-shotgun pistus 4x</t>
+  </si>
+  <si>
+    <t>du pre-shotgun pistus 5x</t>
+  </si>
+  <si>
+    <t>du pre-shotgun pistus 6x</t>
+  </si>
+  <si>
+    <t>du pre-shotgun pistus 7x</t>
+  </si>
+  <si>
+    <t>du pre-shotgun pistus 8x</t>
+  </si>
+  <si>
+    <t>du pre-shotgun pistus x9</t>
+  </si>
+  <si>
+    <t>du pre-shotgun pistus 10x</t>
+  </si>
+  <si>
     <t>du masque de ski</t>
   </si>
   <si>
+    <t>de l'appareil à fondue</t>
+  </si>
+  <si>
+    <t>de l'appareil à raclette</t>
+  </si>
+  <si>
     <t>du Ticket d'or</t>
   </si>
   <si>
+    <t>Oliver Wyman</t>
+  </si>
+  <si>
     <t>di Ticket d'or</t>
   </si>
   <si>
-    <t>Oliver Wyman</t>
-  </si>
-  <si>
-    <t>du pre-shotgun pistus 2x</t>
-  </si>
-  <si>
-    <t>du pre-shotgun pistus 3x</t>
-  </si>
-  <si>
-    <t>du pre-shotgun pistus 4x</t>
-  </si>
-  <si>
-    <t>du pre-shotgun pistus 5x</t>
-  </si>
-  <si>
-    <t>du pre-shotgun pistus 6x</t>
-  </si>
-  <si>
-    <t>du pre-shotgun pistus 7x</t>
-  </si>
-  <si>
-    <t>du pre-shotgun pistus 8x</t>
-  </si>
-  <si>
-    <t>du pre-shotgun pistus x9</t>
-  </si>
-  <si>
-    <t>du pre-shotgun pistus 10x</t>
-  </si>
-  <si>
-    <t>de l'appareil à fondue</t>
-  </si>
-  <si>
-    <t>de l'appareil à raclette</t>
-  </si>
-  <si>
-    <t>personne</t>
-  </si>
-  <si>
-    <t>d'un panier Miam Localpersonne</t>
+    <t>Personne</t>
+  </si>
+  <si>
+    <t>Institut Carlance</t>
+  </si>
+  <si>
+    <t>Viva la vie</t>
+  </si>
+  <si>
+    <t>Brass &amp; Co</t>
+  </si>
+  <si>
+    <t>d'un panier Miam Local</t>
+  </si>
+  <si>
+    <t>Miam Local</t>
+  </si>
+  <si>
+    <t>d'unlot brasserie</t>
+  </si>
+  <si>
+    <t>d'un lot salon de coiffure</t>
+  </si>
+  <si>
+    <t>du massage de 15min Carlance 1x</t>
+  </si>
+  <si>
+    <t>du massage de 15min Carlance 2x</t>
+  </si>
+  <si>
+    <t>du massage de 15min Carlance 3x</t>
+  </si>
+  <si>
+    <t>du massage de 15min Carlance 4x</t>
+  </si>
+  <si>
+    <t>prenoms</t>
+  </si>
+  <si>
+    <t>telephone</t>
+  </si>
+  <si>
+    <t>mail</t>
   </si>
 </sst>
 </file>
@@ -195,7 +234,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -218,13 +257,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -529,10 +582,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -542,156 +595,165 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
         <v>14</v>
       </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
         <v>15</v>
       </c>
-      <c r="B4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
+      <c r="B12" t="s">
         <v>16</v>
       </c>
-      <c r="B5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
+      <c r="C12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
         <v>17</v>
       </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
+      <c r="B13" t="s">
         <v>18</v>
       </c>
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
+      <c r="C13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
         <v>19</v>
       </c>
-      <c r="B8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
+      <c r="B14" t="s">
         <v>20</v>
       </c>
-      <c r="B9" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
+      <c r="C14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
         <v>21</v>
       </c>
-      <c r="B10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
+      <c r="B15" t="s">
         <v>22</v>
       </c>
-      <c r="B11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
+      <c r="C15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
         <v>23</v>
       </c>
-      <c r="B12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
+      <c r="B16" t="s">
         <v>24</v>
-      </c>
-      <c r="B13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" t="s">
-        <v>10</v>
       </c>
       <c r="C16" t="s">
         <v>47</v>
@@ -699,6 +761,9 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" t="s">
         <v>48</v>
       </c>
       <c r="C17" t="s">
@@ -707,10 +772,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s">
         <v>47</v>
@@ -718,10 +783,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="C19" t="s">
         <v>47</v>
@@ -729,10 +794,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s">
         <v>47</v>
@@ -740,10 +802,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
         <v>47</v>
@@ -751,10 +813,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
         <v>47</v>
@@ -762,10 +824,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B23" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="C23" t="s">
         <v>47</v>
@@ -773,10 +835,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C24" t="s">
         <v>47</v>
@@ -784,10 +846,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C25" t="s">
         <v>47</v>
@@ -795,10 +857,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C26" t="s">
         <v>47</v>
@@ -806,10 +868,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B27" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C27" t="s">
         <v>47</v>
@@ -817,10 +879,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B28" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C28" t="s">
         <v>47</v>
@@ -828,10 +890,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B29" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C29" t="s">
         <v>47</v>
@@ -839,10 +901,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B30" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C30" t="s">
         <v>47</v>
@@ -850,10 +912,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B31" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C31" t="s">
         <v>47</v>
@@ -861,10 +923,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B32" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C32" t="s">
         <v>47</v>
@@ -872,10 +934,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B33" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C33" t="s">
         <v>47</v>
@@ -883,10 +945,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B34" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C34" t="s">
         <v>47</v>
@@ -894,12 +956,78 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C35" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" t="s">
+        <v>30</v>
+      </c>
+      <c r="C38" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" t="s">
+        <v>45</v>
+      </c>
+      <c r="C40" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41" t="s">
+        <v>45</v>
+      </c>
+      <c r="C41" t="s">
         <v>47</v>
       </c>
     </row>

--- a/lots.xlsx
+++ b/lots.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathi\Documents\CS\tirage_au_sort_tombola\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB460C23-D7AA-4D3A-9734-749005CFE3E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{563FFD5C-A5CB-4CAD-9A7D-FF15AE2CBC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2460" yWindow="428" windowWidth="19140" windowHeight="12352" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="69">
   <si>
     <t>lots</t>
   </si>
@@ -55,21 +55,9 @@
     <t>du 3ème sac de sport de promo</t>
   </si>
   <si>
-    <t>du 1er bon de 5€ pour pépins</t>
-  </si>
-  <si>
     <t>Impact</t>
   </si>
   <si>
-    <t>du 2ème bon de 5€ pour pépins</t>
-  </si>
-  <si>
-    <t>du 3ème bon de 5€ pour pépins</t>
-  </si>
-  <si>
-    <t>des Chocolats Nepal</t>
-  </si>
-  <si>
     <t>FIR</t>
   </si>
   <si>
@@ -85,9 +73,6 @@
     <t>Commu's</t>
   </si>
   <si>
-    <t>de la place pour le TOSS</t>
-  </si>
-  <si>
     <t>BDS</t>
   </si>
   <si>
@@ -169,24 +154,12 @@
     <t>Institut Carlance</t>
   </si>
   <si>
-    <t>Viva la vie</t>
-  </si>
-  <si>
-    <t>Brass &amp; Co</t>
-  </si>
-  <si>
     <t>d'un panier Miam Local</t>
   </si>
   <si>
     <t>Miam Local</t>
   </si>
   <si>
-    <t>d'unlot brasserie</t>
-  </si>
-  <si>
-    <t>d'un lot salon de coiffure</t>
-  </si>
-  <si>
     <t>du massage de 15min Carlance 1x</t>
   </si>
   <si>
@@ -206,6 +179,54 @@
   </si>
   <si>
     <t>mail</t>
+  </si>
+  <si>
+    <t>du bon de 20€ pépins</t>
+  </si>
+  <si>
+    <t>Macdonald</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d'un plaid </t>
+  </si>
+  <si>
+    <t>d'un bon de reduction de 5€</t>
+  </si>
+  <si>
+    <t>BrassandCo</t>
+  </si>
+  <si>
+    <t>d'un bon de reduction de 10€</t>
+  </si>
+  <si>
+    <t>de 3 verres Coca x1</t>
+  </si>
+  <si>
+    <t>de 3 verres Coca x3</t>
+  </si>
+  <si>
+    <t>de 3 verres Coca x2</t>
+  </si>
+  <si>
+    <t>de 3 verres Coca x4</t>
+  </si>
+  <si>
+    <t>du lot librairie 1x</t>
+  </si>
+  <si>
+    <t>du lot librairie 2x</t>
+  </si>
+  <si>
+    <t>du lot librairie 3x</t>
+  </si>
+  <si>
+    <t>Lagiraf</t>
+  </si>
+  <si>
+    <t>des chocolats de Noël</t>
+  </si>
+  <si>
+    <t>des 2 places pour le TOSS</t>
   </si>
 </sst>
 </file>
@@ -582,7 +603,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -596,13 +617,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -613,7 +634,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
@@ -624,7 +645,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
@@ -635,7 +656,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
@@ -646,7 +667,7 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
@@ -657,7 +678,7 @@
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
@@ -668,40 +689,40 @@
         <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" t="s">
         <v>11</v>
       </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
         <v>14</v>
       </c>
-      <c r="B11" t="s">
-        <v>12</v>
-      </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
@@ -712,323 +733,403 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="B13" t="s">
-        <v>18</v>
-      </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" t="s">
         <v>19</v>
       </c>
-      <c r="B14" t="s">
-        <v>20</v>
-      </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C19" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>58</v>
+        <v>61</v>
+      </c>
+      <c r="B20" t="s">
+        <v>54</v>
       </c>
       <c r="C20" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" t="s">
         <v>54</v>
       </c>
-      <c r="B21" t="s">
-        <v>49</v>
-      </c>
       <c r="C21" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C23" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C24" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="C25" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="C26" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="C27" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="B28" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="C28" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="B29" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="C29" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="B31" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C31" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="B32" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C32" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="B33" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C33" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C34" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C35" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B36" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C36" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="B37" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C37" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B38" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C38" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="B39" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C39" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="B40" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="C40" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="C41" t="s">
-        <v>47</v>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>34</v>
+      </c>
+      <c r="B42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C42" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>35</v>
+      </c>
+      <c r="B43" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>36</v>
+      </c>
+      <c r="B44" t="s">
+        <v>25</v>
+      </c>
+      <c r="C44" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" t="s">
+        <v>25</v>
+      </c>
+      <c r="C45" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>38</v>
+      </c>
+      <c r="B46" t="s">
+        <v>25</v>
+      </c>
+      <c r="C46" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>39</v>
+      </c>
+      <c r="B47" t="s">
+        <v>40</v>
+      </c>
+      <c r="C47" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" t="s">
+        <v>40</v>
+      </c>
+      <c r="C48" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/lots.xlsx
+++ b/lots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathi\Documents\CS\tirage_au_sort_tombola\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51DEFB7A-B608-4D94-A4A0-1C1D8936F962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED1E17B-0636-4CB9-9123-B85BD27A76FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="196">
   <si>
     <t>lots</t>
   </si>
@@ -40,66 +40,198 @@
     <t>mail</t>
   </si>
   <si>
+    <t xml:space="preserve">d'un preshotgun </t>
+  </si>
+  <si>
+    <t>PAPS</t>
+  </si>
+  <si>
+    <t>hosxe</t>
+  </si>
+  <si>
+    <t>come</t>
+  </si>
+  <si>
+    <t>come.hosxe@student-cs.fr</t>
+  </si>
+  <si>
     <t>du Livre : "La colère"</t>
   </si>
   <si>
     <t>BDA</t>
   </si>
   <si>
+    <t>Burlinchon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dimitri </t>
+  </si>
+  <si>
+    <t>dimitri.burlinchon@student-cs.fr</t>
+  </si>
+  <si>
     <t>du Livre : "Chienne de vie"</t>
   </si>
   <si>
+    <t>Ducruit</t>
+  </si>
+  <si>
+    <t>thibault</t>
+  </si>
+  <si>
+    <t>thibault.ducruit@student-cs.fr</t>
+  </si>
+  <si>
     <t>du Livre : "sous les feux d'artifice"</t>
   </si>
   <si>
+    <t>Roy</t>
+  </si>
+  <si>
+    <t>Nathan</t>
+  </si>
+  <si>
+    <t>nathan.roy@student-cs.fr</t>
+  </si>
+  <si>
     <t>du 1er sac de sport de promo</t>
   </si>
   <si>
     <t>BDE</t>
   </si>
   <si>
+    <t>Benoit</t>
+  </si>
+  <si>
+    <t>Baptiste</t>
+  </si>
+  <si>
+    <t>baptiste.benoit@student-cs.fr</t>
+  </si>
+  <si>
     <t>du 2ème sac de sport de promo</t>
   </si>
   <si>
+    <t>Pradeau</t>
+  </si>
+  <si>
+    <t>Domitille</t>
+  </si>
+  <si>
+    <t>domitille.pradeau@student-cs.fr</t>
+  </si>
+  <si>
     <t>du 3ème sac de sport de promo</t>
   </si>
   <si>
+    <t>Barsalou</t>
+  </si>
+  <si>
+    <t>Quentin</t>
+  </si>
+  <si>
+    <t>quentbarsa@gmail.com</t>
+  </si>
+  <si>
     <t>du bon de 20€ pépins</t>
   </si>
   <si>
     <t>Impact</t>
   </si>
   <si>
+    <t>Charley</t>
+  </si>
+  <si>
+    <t>Aubin</t>
+  </si>
+  <si>
+    <t>aubin.charley@gmail.com</t>
+  </si>
+  <si>
     <t>des chocolats de Noël</t>
   </si>
   <si>
     <t>FIR</t>
   </si>
   <si>
+    <t>Albert</t>
+  </si>
+  <si>
+    <t>Thomas</t>
+  </si>
+  <si>
+    <t>thomas.albert@student-cs.fr</t>
+  </si>
+  <si>
+    <t>du bon de 15€ pépins</t>
+  </si>
+  <si>
+    <t>Reymondie</t>
+  </si>
+  <si>
+    <t>thomas.reymondie@student-cs.fr</t>
+  </si>
+  <si>
     <t>des 2 places pour le NND</t>
   </si>
   <si>
     <t>RAID</t>
   </si>
   <si>
+    <t>Burtin</t>
+  </si>
+  <si>
+    <t>Benjamin</t>
+  </si>
+  <si>
+    <t>benjamin.burtin@student-cs.fr</t>
+  </si>
+  <si>
     <t>des 2 places pour la commu's</t>
   </si>
   <si>
     <t>Commu's</t>
   </si>
   <si>
+    <t>MASTERNAK</t>
+  </si>
+  <si>
+    <t>Célia</t>
+  </si>
+  <si>
+    <t>celia.masternak@hotmail.fr</t>
+  </si>
+  <si>
     <t>des 2 places pour le TOSS</t>
   </si>
   <si>
     <t>BDS</t>
   </si>
   <si>
+    <t>Goudon</t>
+  </si>
+  <si>
+    <t>Oscar</t>
+  </si>
+  <si>
+    <t>oscar.goudon-de-lalande@student-cs.fr</t>
+  </si>
+  <si>
     <t>des impressions de 5 photos</t>
   </si>
   <si>
     <t>PICS</t>
   </si>
   <si>
+    <t xml:space="preserve">Terrasson </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arthur </t>
+  </si>
+  <si>
+    <t>arthur.terrasson@free.fr</t>
+  </si>
+  <si>
     <t>du massage de 15min Carlance 1x</t>
   </si>
   <si>
@@ -109,121 +241,373 @@
     <t>du massage de 15min Carlance 2x</t>
   </si>
   <si>
+    <t>lethuillier</t>
+  </si>
+  <si>
+    <t>justine</t>
+  </si>
+  <si>
+    <t>justine.lethuillier@student-cs.fr</t>
+  </si>
+  <si>
     <t>du massage de 15min Carlance 3x</t>
   </si>
   <si>
+    <t>Haddad</t>
+  </si>
+  <si>
+    <t>Emett</t>
+  </si>
+  <si>
+    <t>emett.haddad@ens-paris-saclay.fr</t>
+  </si>
+  <si>
     <t>du massage de 15min Carlance 4x</t>
   </si>
   <si>
+    <t xml:space="preserve">Flamand </t>
+  </si>
+  <si>
+    <t>thomas.flamand@student-cs.fr</t>
+  </si>
+  <si>
     <t>de 3 verres Coca x1</t>
   </si>
   <si>
-    <t>Macdonald</t>
+    <t>Mcdonald</t>
+  </si>
+  <si>
+    <t>Denis</t>
+  </si>
+  <si>
+    <t>Edgar</t>
+  </si>
+  <si>
+    <t>edgar.denis@student-cs.fr</t>
   </si>
   <si>
     <t>de 3 verres Coca x2</t>
   </si>
   <si>
+    <t>Mauhourat</t>
+  </si>
+  <si>
+    <t>Adrien</t>
+  </si>
+  <si>
+    <t>adrien.m798@gmail.com</t>
+  </si>
+  <si>
     <t>de 3 verres Coca x3</t>
   </si>
   <si>
+    <t xml:space="preserve">Bekrar </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ziyad </t>
+  </si>
+  <si>
+    <t>ziyad94240@gmail.com</t>
+  </si>
+  <si>
     <t>de 3 verres Coca x4</t>
   </si>
   <si>
+    <t>Petit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">François </t>
+  </si>
+  <si>
+    <t>francois.petit@student-cs.fr</t>
+  </si>
+  <si>
     <t xml:space="preserve">d'un plaid </t>
   </si>
   <si>
+    <t>Pisarik</t>
+  </si>
+  <si>
+    <t>Jan</t>
+  </si>
+  <si>
+    <t>jan.pisarik23@gmail.com</t>
+  </si>
+  <si>
     <t>d'un bon de reduction de 5€</t>
   </si>
   <si>
     <t>BrassandCo</t>
   </si>
   <si>
+    <t>Brandel</t>
+  </si>
+  <si>
+    <t>Nicolas</t>
+  </si>
+  <si>
+    <t>nicolas.brandel@student-cs.fr</t>
+  </si>
+  <si>
     <t>d'un bon de reduction de 10€</t>
   </si>
   <si>
+    <t>Dumortier</t>
+  </si>
+  <si>
+    <t>Julien</t>
+  </si>
+  <si>
+    <t>julien.dumortier@student-cs.fr</t>
+  </si>
+  <si>
     <t>du lot librairie 1x</t>
   </si>
   <si>
     <t>Lagiraf</t>
   </si>
   <si>
+    <t>Brugère</t>
+  </si>
+  <si>
+    <t>Raphaël</t>
+  </si>
+  <si>
+    <t>raphael.brugere06@gmail.com</t>
+  </si>
+  <si>
     <t>du lot librairie 2x</t>
   </si>
   <si>
     <t>du lot librairie 3x</t>
   </si>
   <si>
+    <t>Moutet</t>
+  </si>
+  <si>
+    <t>Thibault</t>
+  </si>
+  <si>
+    <t>thibault.moutet@student-cs.fr</t>
+  </si>
+  <si>
     <t>d'un panier Miam Local</t>
   </si>
   <si>
     <t>Miam Local</t>
   </si>
   <si>
+    <t>Houri</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>dadahouri@gmail.com</t>
+  </si>
+  <si>
     <t>du casque audio ou de la cotiz VR</t>
   </si>
   <si>
     <t>Viarezo</t>
   </si>
   <si>
+    <t>Perdreau</t>
+  </si>
+  <si>
+    <t>thomas.perdreau@student-cs.fr</t>
+  </si>
+  <si>
     <t>de la Bouteille de champagne</t>
   </si>
   <si>
     <t>JCS</t>
   </si>
   <si>
+    <t>Huber</t>
+  </si>
+  <si>
+    <t>Gaston</t>
+  </si>
+  <si>
+    <t>gaston.huber@student-cs.fr</t>
+  </si>
+  <si>
     <t>du Bonnet</t>
   </si>
   <si>
     <t>WACS</t>
   </si>
   <si>
+    <t>Valade</t>
+  </si>
+  <si>
+    <t>Corentin</t>
+  </si>
+  <si>
+    <t>corentin.valade@student-cs.fr</t>
+  </si>
+  <si>
     <t>du pre-shotgun pistus 1x</t>
   </si>
   <si>
+    <t>Charrondiere</t>
+  </si>
+  <si>
+    <t>nicolas.charrondiere@student-cs.fr</t>
+  </si>
+  <si>
     <t>du pre-shotgun pistus 2x</t>
   </si>
   <si>
+    <t>Corrard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alexandre </t>
+  </si>
+  <si>
+    <t>alexandre.corrard@student-cs.fr</t>
+  </si>
+  <si>
     <t>du pre-shotgun pistus 3x</t>
   </si>
   <si>
     <t>du pre-shotgun pistus 4x</t>
   </si>
   <si>
+    <t xml:space="preserve">Gaudichau </t>
+  </si>
+  <si>
+    <t>Alix</t>
+  </si>
+  <si>
+    <t>alix.gaudichau@student-cs.fr</t>
+  </si>
+  <si>
     <t>du pre-shotgun pistus 5x</t>
   </si>
   <si>
+    <t xml:space="preserve">Gabalda </t>
+  </si>
+  <si>
+    <t>Philippine</t>
+  </si>
+  <si>
+    <t>philippine.gabalda@student-cs.fr</t>
+  </si>
+  <si>
     <t>du pre-shotgun pistus 6x</t>
   </si>
   <si>
+    <t xml:space="preserve">Dzouossia Mozie </t>
+  </si>
+  <si>
+    <t>Keli Xaviera</t>
+  </si>
+  <si>
+    <t>keli-xaviera.dzouossia-mozie@student-cs.fr</t>
+  </si>
+  <si>
     <t>du pre-shotgun pistus 7x</t>
   </si>
   <si>
+    <t>Lyonnais</t>
+  </si>
+  <si>
+    <t>Maximilien</t>
+  </si>
+  <si>
+    <t>maximilien.lyonnais@hotmail.fr</t>
+  </si>
+  <si>
     <t>du pre-shotgun pistus 8x</t>
   </si>
   <si>
+    <t>Audap</t>
+  </si>
+  <si>
+    <t>Florent</t>
+  </si>
+  <si>
+    <t>florent.audap@student-cs.fr</t>
+  </si>
+  <si>
     <t>du pre-shotgun pistus x9</t>
   </si>
   <si>
+    <t>Riclet</t>
+  </si>
+  <si>
+    <t>Titouan</t>
+  </si>
+  <si>
+    <t>titouan.riclet@student-cs.fr</t>
+  </si>
+  <si>
     <t>du pre-shotgun pistus 10x</t>
   </si>
   <si>
+    <t>Le Meur</t>
+  </si>
+  <si>
+    <t>Robin</t>
+  </si>
+  <si>
+    <t>robin.lemeur@student-cs.fr</t>
+  </si>
+  <si>
     <t>du masque de ski</t>
   </si>
   <si>
     <t>de l'appareil à fondue</t>
   </si>
   <si>
+    <t xml:space="preserve">Rabinovitch </t>
+  </si>
+  <si>
+    <t>Sami</t>
+  </si>
+  <si>
+    <t>sami.rabinovitch@student-cs.fr</t>
+  </si>
+  <si>
     <t>de l'appareil à raclette</t>
   </si>
   <si>
+    <t>de Malherbe</t>
+  </si>
+  <si>
+    <t>Gauthier</t>
+  </si>
+  <si>
+    <t>gauthierdemalherbe@gmail.com</t>
+  </si>
+  <si>
     <t>du Ticket d'or</t>
   </si>
   <si>
     <t>Oliver Wyman</t>
   </si>
   <si>
+    <t>Knecht</t>
+  </si>
+  <si>
+    <t>Axel</t>
+  </si>
+  <si>
+    <t>axel.knecht@outlook.fr</t>
+  </si>
+  <si>
     <t>di Ticket d'or</t>
+  </si>
+  <si>
+    <t>François</t>
+  </si>
+  <si>
+    <t>Martin</t>
+  </si>
+  <si>
+    <t>martin.francois@student-cs.fr</t>
   </si>
 </sst>
 </file>
@@ -586,7 +970,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -616,365 +1000,957 @@
       <c r="B3" t="s">
         <v>7</v>
       </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3">
+        <v>33651483017</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4">
+        <v>33762266066</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5">
+        <v>33623308472</v>
+      </c>
+      <c r="F5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6">
+        <v>33684459945</v>
+      </c>
+      <c r="F6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7">
+        <v>33679498204</v>
+      </c>
+      <c r="F7" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8">
+        <v>33620055631</v>
+      </c>
+      <c r="F8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9">
+        <v>33637762753</v>
+      </c>
+      <c r="F9" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>38</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10">
+        <v>33619660034</v>
+      </c>
+      <c r="F10" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>43</v>
+      </c>
+      <c r="C11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11">
+        <v>33624175857</v>
+      </c>
+      <c r="F11" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>43</v>
+      </c>
+      <c r="C12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12">
+        <v>33659565510</v>
+      </c>
+      <c r="F12" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>51</v>
+      </c>
+      <c r="C13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13">
+        <v>33651600744</v>
+      </c>
+      <c r="F13" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>56</v>
+      </c>
+      <c r="C14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14">
+        <v>33601862716</v>
+      </c>
+      <c r="F14" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>61</v>
+      </c>
+      <c r="C15" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15">
+        <v>33767212208</v>
+      </c>
+      <c r="F15" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+      <c r="C16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16">
+        <v>33766107291</v>
+      </c>
+      <c r="F16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+        <v>71</v>
+      </c>
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17">
+        <v>33684459945</v>
+      </c>
+      <c r="F17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+        <v>71</v>
+      </c>
+      <c r="C18" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18">
+        <v>33784318416</v>
+      </c>
+      <c r="F18" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+        <v>71</v>
+      </c>
+      <c r="C19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19">
+        <v>33652811004</v>
+      </c>
+      <c r="F19" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+        <v>71</v>
+      </c>
+      <c r="C20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20">
+        <v>33788206620</v>
+      </c>
+      <c r="F20" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" t="s">
+        <v>85</v>
+      </c>
+      <c r="D21" t="s">
+        <v>86</v>
+      </c>
+      <c r="E21">
+        <v>33651757880</v>
+      </c>
+      <c r="F21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" t="s">
+        <v>84</v>
+      </c>
+      <c r="C22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" t="s">
+        <v>90</v>
+      </c>
+      <c r="E22">
+        <v>33761753259</v>
+      </c>
+      <c r="F22" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B23" t="s">
+        <v>84</v>
+      </c>
+      <c r="C23" t="s">
+        <v>93</v>
+      </c>
+      <c r="D23" t="s">
+        <v>94</v>
+      </c>
+      <c r="E23">
+        <v>33625827673</v>
+      </c>
+      <c r="F23" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24">
+        <v>33769590556</v>
+      </c>
+      <c r="F24" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>100</v>
+      </c>
+      <c r="B25" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" t="s">
+        <v>101</v>
+      </c>
+      <c r="D25" t="s">
+        <v>102</v>
+      </c>
+      <c r="E25">
+        <v>33768643864</v>
+      </c>
+      <c r="F25" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>104</v>
+      </c>
+      <c r="B26" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26">
+        <v>33624175857</v>
+      </c>
+      <c r="F26" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>104</v>
+      </c>
+      <c r="B27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C27" t="s">
+        <v>106</v>
+      </c>
+      <c r="D27" t="s">
+        <v>107</v>
+      </c>
+      <c r="E27">
+        <v>33766517724</v>
+      </c>
+      <c r="F27" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>109</v>
+      </c>
+      <c r="B28" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" t="s">
+        <v>111</v>
+      </c>
+      <c r="E28">
+        <v>33782026818</v>
+      </c>
+      <c r="F28" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" t="s">
+        <v>115</v>
+      </c>
+      <c r="D29" t="s">
+        <v>116</v>
+      </c>
+      <c r="E29">
+        <v>33629444951</v>
+      </c>
+      <c r="F29" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>118</v>
+      </c>
+      <c r="B30" t="s">
+        <v>114</v>
+      </c>
+      <c r="C30" t="s">
         <v>34</v>
       </c>
-      <c r="B21" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
+      <c r="D30" t="s">
         <v>35</v>
       </c>
-      <c r="B22" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
+      <c r="E30">
+        <v>33637762753</v>
+      </c>
+      <c r="F30" t="s">
         <v>36</v>
       </c>
-      <c r="B23" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
-        <v>44</v>
-      </c>
-      <c r="B30" t="s">
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>119</v>
+      </c>
+      <c r="B31" t="s">
+        <v>114</v>
+      </c>
+      <c r="C31" t="s">
+        <v>120</v>
+      </c>
+      <c r="D31" t="s">
+        <v>121</v>
+      </c>
+      <c r="E31">
+        <v>33782610302</v>
+      </c>
+      <c r="F31" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>123</v>
+      </c>
+      <c r="B32" t="s">
+        <v>124</v>
+      </c>
+      <c r="C32" t="s">
+        <v>125</v>
+      </c>
+      <c r="D32" t="s">
+        <v>126</v>
+      </c>
+      <c r="E32">
+        <v>33781803803</v>
+      </c>
+      <c r="F32" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>128</v>
+      </c>
+      <c r="B33" t="s">
+        <v>129</v>
+      </c>
+      <c r="C33" t="s">
+        <v>130</v>
+      </c>
+      <c r="D33" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
-        <v>46</v>
-      </c>
-      <c r="B31" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A32" t="s">
-        <v>48</v>
-      </c>
-      <c r="B32" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
-        <v>50</v>
-      </c>
-      <c r="B33" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="E33">
+        <v>33651313404</v>
+      </c>
+      <c r="F33" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>52</v>
+        <v>132</v>
       </c>
       <c r="B34" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+        <v>133</v>
+      </c>
+      <c r="C34" t="s">
+        <v>134</v>
+      </c>
+      <c r="D34" t="s">
+        <v>135</v>
+      </c>
+      <c r="E34">
+        <v>33767280074</v>
+      </c>
+      <c r="F34" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>53</v>
+        <v>137</v>
       </c>
       <c r="B35" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+        <v>138</v>
+      </c>
+      <c r="C35" t="s">
+        <v>139</v>
+      </c>
+      <c r="D35" t="s">
+        <v>140</v>
+      </c>
+      <c r="E35">
+        <v>33636499097</v>
+      </c>
+      <c r="F35" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="B36" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+        <v>138</v>
+      </c>
+      <c r="C36" t="s">
+        <v>143</v>
+      </c>
+      <c r="D36" t="s">
+        <v>107</v>
+      </c>
+      <c r="E36">
+        <v>33781361341</v>
+      </c>
+      <c r="F36" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>55</v>
+        <v>145</v>
       </c>
       <c r="B37" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+        <v>138</v>
+      </c>
+      <c r="C37" t="s">
+        <v>146</v>
+      </c>
+      <c r="D37" t="s">
+        <v>147</v>
+      </c>
+      <c r="E37">
+        <v>33663462732</v>
+      </c>
+      <c r="F37" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>56</v>
+        <v>149</v>
       </c>
       <c r="B38" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+        <v>138</v>
+      </c>
+      <c r="C38" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38" t="s">
+        <v>18</v>
+      </c>
+      <c r="E38">
+        <v>33623308472</v>
+      </c>
+      <c r="F38" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>57</v>
+        <v>150</v>
       </c>
       <c r="B39" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+        <v>138</v>
+      </c>
+      <c r="C39" t="s">
+        <v>151</v>
+      </c>
+      <c r="D39" t="s">
+        <v>152</v>
+      </c>
+      <c r="E39">
+        <v>33698888321</v>
+      </c>
+      <c r="F39" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>58</v>
+        <v>154</v>
       </c>
       <c r="B40" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+        <v>138</v>
+      </c>
+      <c r="C40" t="s">
+        <v>155</v>
+      </c>
+      <c r="D40" t="s">
+        <v>156</v>
+      </c>
+      <c r="E40">
+        <v>33672160897</v>
+      </c>
+      <c r="F40" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>59</v>
+        <v>158</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+        <v>138</v>
+      </c>
+      <c r="C41" t="s">
+        <v>159</v>
+      </c>
+      <c r="D41" t="s">
+        <v>160</v>
+      </c>
+      <c r="E41">
+        <v>33753348558</v>
+      </c>
+      <c r="F41" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>60</v>
+        <v>162</v>
       </c>
       <c r="B42" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+        <v>138</v>
+      </c>
+      <c r="C42" t="s">
+        <v>163</v>
+      </c>
+      <c r="D42" t="s">
+        <v>164</v>
+      </c>
+      <c r="E42">
+        <v>33642159186</v>
+      </c>
+      <c r="F42" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>61</v>
+        <v>166</v>
       </c>
       <c r="B43" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+        <v>138</v>
+      </c>
+      <c r="C43" t="s">
+        <v>167</v>
+      </c>
+      <c r="D43" t="s">
+        <v>168</v>
+      </c>
+      <c r="E43">
+        <v>33777780369</v>
+      </c>
+      <c r="F43" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>62</v>
+        <v>170</v>
       </c>
       <c r="B44" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+        <v>138</v>
+      </c>
+      <c r="C44" t="s">
+        <v>171</v>
+      </c>
+      <c r="D44" t="s">
+        <v>172</v>
+      </c>
+      <c r="E44">
+        <v>33640913307</v>
+      </c>
+      <c r="F44" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>63</v>
+        <v>174</v>
       </c>
       <c r="B45" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+        <v>138</v>
+      </c>
+      <c r="C45" t="s">
+        <v>175</v>
+      </c>
+      <c r="D45" t="s">
+        <v>176</v>
+      </c>
+      <c r="E45">
+        <v>33768553797</v>
+      </c>
+      <c r="F45" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>64</v>
+        <v>178</v>
       </c>
       <c r="B46" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+        <v>138</v>
+      </c>
+      <c r="C46" t="s">
+        <v>155</v>
+      </c>
+      <c r="D46" t="s">
+        <v>156</v>
+      </c>
+      <c r="E46">
+        <v>33672160897</v>
+      </c>
+      <c r="F46" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>65</v>
+        <v>179</v>
       </c>
       <c r="B47" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+        <v>138</v>
+      </c>
+      <c r="C47" t="s">
+        <v>180</v>
+      </c>
+      <c r="D47" t="s">
+        <v>181</v>
+      </c>
+      <c r="E47">
+        <v>33601205378</v>
+      </c>
+      <c r="F47" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>67</v>
+        <v>183</v>
       </c>
       <c r="B48" t="s">
-        <v>66</v>
+        <v>138</v>
+      </c>
+      <c r="C48" t="s">
+        <v>184</v>
+      </c>
+      <c r="D48" t="s">
+        <v>185</v>
+      </c>
+      <c r="E48">
+        <v>33699193332</v>
+      </c>
+      <c r="F48" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>187</v>
+      </c>
+      <c r="B49" t="s">
+        <v>188</v>
+      </c>
+      <c r="C49" t="s">
+        <v>189</v>
+      </c>
+      <c r="D49" t="s">
+        <v>190</v>
+      </c>
+      <c r="E49">
+        <v>33675105625</v>
+      </c>
+      <c r="F49" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>192</v>
+      </c>
+      <c r="B50" t="s">
+        <v>188</v>
+      </c>
+      <c r="C50" t="s">
+        <v>193</v>
+      </c>
+      <c r="D50" t="s">
+        <v>194</v>
+      </c>
+      <c r="E50">
+        <v>33618976097</v>
+      </c>
+      <c r="F50" t="s">
+        <v>195</v>
       </c>
     </row>
   </sheetData>
